--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559177.2821848005</v>
+        <v>559177</v>
       </c>
       <c r="R2" t="n">
-        <v>6248384.082623001</v>
+        <v>6248384</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559177.2821848005</v>
+        <v>559177</v>
       </c>
       <c r="R3" t="n">
-        <v>6248384.082623001</v>
+        <v>6248384</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>104493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559177.2821848005</v>
+        <v>559177</v>
       </c>
       <c r="R4" t="n">
-        <v>6248384.082623001</v>
+        <v>6248384</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558978.3924896313</v>
+        <v>558978</v>
       </c>
       <c r="R5" t="n">
-        <v>6248281.643851819</v>
+        <v>6248282</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>106994</v>
+        <v>107003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110713</v>
+        <v>110722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107003</v>
+        <v>107008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110722</v>
+        <v>110727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107008</v>
+        <v>107036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110727</v>
+        <v>110755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107036</v>
+        <v>107042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110755</v>
+        <v>110761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107042</v>
+        <v>107049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110761</v>
+        <v>110768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107049</v>
+        <v>107053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110768</v>
+        <v>110772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107053</v>
+        <v>107061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110772</v>
+        <v>110780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101723</v>
+        <v>101728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107064</v>
+        <v>107069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110783</v>
+        <v>110788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101728</v>
+        <v>101736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107069</v>
+        <v>107077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110788</v>
+        <v>110796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471951</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74561547</v>
       </c>
       <c r="B3" t="n">
-        <v>101736</v>
+        <v>101746</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74624585</v>
       </c>
       <c r="B4" t="n">
-        <v>107077</v>
+        <v>107087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74977375</v>
       </c>
       <c r="B5" t="n">
-        <v>110796</v>
+        <v>110806</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28946-2025 artfynd.xlsx
+++ b/artfynd/A 28946-2025 artfynd.xlsx
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74471951</v>
+        <v>74624585</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>107611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1897</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>L16 Juanslycke vägkors 500 m ONO, Sm</t>
+          <t>L79 Stensborg 650 m ONO t NO, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 3G9b 4844. SOM: Hepatica nobilis. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 3G9b 4844. SOM: Melampyrum cristatum. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sänka i lövskog</t>
+          <t>Sydvänt ekskogsbryn</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74561547</v>
+        <v>74977375</v>
       </c>
       <c r="B3" t="n">
-        <v>101746</v>
+        <v>111398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221223</v>
+        <v>219716</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>L79 Stensborg 650 m ONO t NO, Sm</t>
+          <t>L76 Stensborg 400 m NO, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559177</v>
+        <v>558978</v>
       </c>
       <c r="R3" t="n">
-        <v>6248384</v>
+        <v>6248282</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 3G9b 4844. SOM: Lathyrus niger. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 3G9b 4742. SOM: Selinum carvifolia. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Ekbacke</t>
+          <t>Slåttermark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74624585</v>
+        <v>74561547</v>
       </c>
       <c r="B4" t="n">
-        <v>107087</v>
+        <v>102224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1897</v>
+        <v>221223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 3G9b 4844. SOM: Melampyrum cristatum. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 3G9b 4844. SOM: Lathyrus niger. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Sydvänt ekskogsbryn</t>
+          <t>Ekbacke</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,45 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74977375</v>
+        <v>74471951</v>
       </c>
       <c r="B5" t="n">
-        <v>110806</v>
+        <v>101325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219716</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>L76 Stensborg 400 m NO, Sm</t>
+          <t>L16 Juanslycke vägkors 500 m ONO, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558978</v>
+        <v>559177</v>
       </c>
       <c r="R5" t="n">
-        <v>6248282</v>
+        <v>6248384</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 3G9b 4742. SOM: Selinum carvifolia. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 3G9b 4844. SOM: Hepatica nobilis. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Slåttermark</t>
+          <t>Sänka i lövskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
